--- a/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/01_bao_cao_ca_ban_hang.xlsx
+++ b/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/01_bao_cao_ca_ban_hang.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="Rfbcb6ec818324556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.2026" sheetId="2" r:id="Rec88eb481ad24014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.2026" sheetId="3" r:id="R915ead289b8643b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.2026" sheetId="4" r:id="R7c023341f09f4479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R86a090678ecb4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.2026" sheetId="2" r:id="R08219df74eef4d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.2026" sheetId="3" r:id="R8edcec2b9c4049cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.2026" sheetId="4" r:id="Rc0988e82859a48b5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/01_bao_cao_ca_ban_hang.xlsx
+++ b/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/01_bao_cao_ca_ban_hang.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R86a090678ecb4b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.2026" sheetId="2" r:id="R08219df74eef4d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.2026" sheetId="3" r:id="R8edcec2b9c4049cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.2026" sheetId="4" r:id="Rc0988e82859a48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R347d82be8e064981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.2026" sheetId="2" r:id="R371a746fa03245a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.2026" sheetId="3" r:id="R334a42c986a348f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.2026" sheetId="4" r:id="Rcb5531e4096a4574"/>
   </x:sheets>
 </x:workbook>
 </file>
